--- a/start-iids/data/reference/RP7.3_calculation_log.xlsx
+++ b/start-iids/data/reference/RP7.3_calculation_log.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calculation_log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ahp" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="calculation_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ahp" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NOTE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
+          <t>(RI_ref[2022 Jan-Jul]-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref) [ADR-015 option A]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14138.28</v>
+        <v>8864.7016</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..) [ADR-015 option A: ref=2022 Jan-Jul]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>16277.148</v>
+        <v>10205.7718</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..) [ADR-015 option A: ref=2022 Jan-Jul]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10114.308</v>
+        <v>6341.6711</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO [ADR-015 option A: ref=2022 Jan-Jul]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12134.7528</v>
+        <v>7608.4901</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>52664.4888</v>
+        <v>33020.6346</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>13276.3196</v>
+        <v>8325.034299999999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ex_el+Ex_fuel</t>
+          <t>Ex_el+Ex_fuel (period Jan-Jul 2025)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>184300</v>
+        <v>115556.0952</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3616</v>
+        <v>1.3613</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.2</t>
         </is>
       </c>
     </row>

--- a/start-iids/data/reference/RP7.3_calculation_log.xlsx
+++ b/start-iids/data/reference/RP7.3_calculation_log.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8864.7016</v>
+        <v>18458.07</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10205.7718</v>
+        <v>4735.62</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6341.6711</v>
+        <v>3341.53</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7608.4901</v>
+        <v>3187.83</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>33020.6346</v>
+        <v>29723.05</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8325.034299999999</v>
+        <v>9017.846299999999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>115556.0952</v>
+        <v>114990.012</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.118</v>
+        <v>0.1212</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3613</v>
+        <v>1.3981</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>beta-1.2</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>

--- a/start-iids/data/reference/RP7.3_calculation_log.xlsx
+++ b/start-iids/data/reference/RP7.3_calculation_log.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calculation_log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ahp" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="calculation_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ahp" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NOTE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
+          <t>(RI_ref[2022 Jan-Jul]-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref) [ADR-015 option A]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14138.28</v>
+        <v>18458.07</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..) [ADR-015 option A: ref=2022 Jan-Jul]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>16277.148</v>
+        <v>4735.62</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..) [ADR-015 option A: ref=2022 Jan-Jul]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10114.308</v>
+        <v>3341.53</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO [ADR-015 option A: ref=2022 Jan-Jul]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12134.7528</v>
+        <v>3187.83</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>52664.4888</v>
+        <v>29723.05</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>13276.3196</v>
+        <v>9017.846299999999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ex_el+Ex_fuel</t>
+          <t>Ex_el+Ex_fuel (period Jan-Jul 2025)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>184300</v>
+        <v>114990.012</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.118</v>
+        <v>0.1212</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3616</v>
+        <v>1.3981</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>beta-1.1</t>
+          <t>beta-1.3</t>
         </is>
       </c>
     </row>
